--- a/stories/arbres/TREE-AUT-027.xlsx
+++ b/stories/arbres/TREE-AUT-027.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Tom est avec papa, au marché. Tom a envie de jouer. papa est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom écoute papa. Tom entend les mots : manteau, sortir, rentrer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On dit merci. papa dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On dit merci. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On dit merci.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Tom respire. Tom retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2234,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2353,6 +2401,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2543,6 +2596,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2705,6 +2763,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Le sol est un peu froid. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2867,6 +2930,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3029,6 +3097,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Une feuille tombe. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3191,6 +3264,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3353,6 +3431,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3515,6 +3598,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3677,6 +3765,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3867,6 +3960,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4029,6 +4127,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Une feuille tombe. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4191,6 +4294,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4353,6 +4461,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4515,6 +4628,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4677,6 +4795,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4839,6 +4962,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5001,6 +5129,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5191,6 +5324,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5353,6 +5491,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5515,6 +5658,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5677,6 +5825,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5839,6 +5992,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6001,6 +6159,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6163,6 +6326,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6187,7 +6355,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On souffle doucement. papa dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On souffle doucement. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6325,6 +6493,12 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On souffle doucement.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6505,6 +6679,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
     </row>
@@ -6673,6 +6852,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Tom respire. Tom retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6863,6 +7047,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7025,6 +7214,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7215,6 +7409,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7377,6 +7576,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7539,6 +7743,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7701,6 +7910,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7863,6 +8077,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8025,6 +8244,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8187,6 +8411,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8349,6 +8578,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8539,6 +8773,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8701,6 +8940,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8863,6 +9107,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9025,6 +9274,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9187,6 +9441,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9349,6 +9608,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. La lumière est claire. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9511,6 +9775,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9673,6 +9942,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9863,6 +10137,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10025,6 +10304,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10187,6 +10471,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10349,6 +10638,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10511,6 +10805,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10673,6 +10972,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10835,6 +11139,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10859,7 +11168,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On écoute jusqu'au bout. papa dit : je suis là. On reste ensemble.</t>
+          <t>Tom va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10997,6 +11306,12 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Tom va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On écoute jusqu'au bout.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11177,6 +11492,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
     </row>
@@ -11345,6 +11665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Tom respire. Tom retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11535,6 +11860,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11697,6 +12027,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11887,6 +12222,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12049,6 +12389,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12211,6 +12556,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12373,6 +12723,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12535,6 +12890,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12697,6 +13057,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12859,6 +13224,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13021,6 +13391,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13211,6 +13586,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13373,6 +13753,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13535,6 +13920,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13697,6 +14087,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. La lumière est claire. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13859,6 +14254,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14021,6 +14421,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14183,6 +14588,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14345,6 +14755,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Tom a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On rit un peu. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14535,6 +14950,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14697,6 +15117,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le matin. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14859,6 +15284,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15021,6 +15451,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint après la sieste. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15183,6 +15618,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15345,6 +15785,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Tom rejoint le soir. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15507,6 +15952,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15525,7 +15975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15542,6 +15992,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-027.xlsx
+++ b/stories/arbres/TREE-AUT-027.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Tom est avec papa, au marché. Tom a envie de jouer. papa est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom écoute papa. Tom entend les mots : manteau, sortir, rentrer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Tom respire. Tom retient : manteau, sortir, rentrer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2239,6 +2249,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2406,6 +2417,7 @@
           <t>narrateur|Tom a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2601,6 +2613,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2768,6 +2781,7 @@
           <t>narrateur|Tom rejoint le matin. Le sol est un peu froid. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2935,6 +2949,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3102,6 +3117,7 @@
           <t>narrateur|Tom rejoint après la sieste. Une feuille tombe. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3269,6 +3285,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3436,6 +3453,7 @@
           <t>narrateur|Tom rejoint le soir. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3603,6 +3621,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3770,6 +3789,7 @@
           <t>narrateur|Tom a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3965,6 +3985,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4132,6 +4153,7 @@
           <t>narrateur|Tom rejoint le matin. Une feuille tombe. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4299,6 +4321,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4466,6 +4489,7 @@
           <t>narrateur|Tom rejoint après la sieste. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4633,6 +4657,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4800,6 +4825,7 @@
           <t>narrateur|Tom rejoint le soir. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4967,6 +4993,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5134,6 +5161,7 @@
           <t>narrateur|Tom a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5329,6 +5357,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5496,6 +5525,7 @@
           <t>narrateur|Tom rejoint le matin. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5663,6 +5693,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5830,6 +5861,7 @@
           <t>narrateur|Tom rejoint après la sieste. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5997,6 +6029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6164,6 +6197,7 @@
           <t>narrateur|Tom rejoint le soir. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6331,6 +6365,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6499,6 +6534,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6686,6 +6722,7 @@
           <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6857,6 +6894,7 @@
           <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Tom respire. Tom retient : manteau, sortir, rentrer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7052,6 +7090,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7219,6 +7258,7 @@
           <t>narrateur|Tom a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7414,6 +7454,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7581,6 +7622,7 @@
           <t>narrateur|Tom rejoint le matin. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7748,6 +7790,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7915,6 +7958,7 @@
           <t>narrateur|Tom rejoint après la sieste. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8082,6 +8126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8249,6 +8294,7 @@
           <t>narrateur|Tom rejoint le soir. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8416,6 +8462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8583,6 +8630,7 @@
           <t>narrateur|Tom a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8778,6 +8826,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8945,6 +8994,7 @@
           <t>narrateur|Tom rejoint le matin. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9112,6 +9162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9279,6 +9330,7 @@
           <t>narrateur|Tom rejoint après la sieste. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9446,6 +9498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9613,6 +9666,7 @@
           <t>narrateur|Tom rejoint le soir. La lumière est claire. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9780,6 +9834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9947,6 +10002,7 @@
           <t>narrateur|Tom a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10142,6 +10198,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10309,6 +10366,7 @@
           <t>narrateur|Tom rejoint le matin. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10476,6 +10534,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10643,6 +10702,7 @@
           <t>narrateur|Tom rejoint après la sieste. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10810,6 +10870,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10977,6 +11038,7 @@
           <t>narrateur|Tom rejoint le soir. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11144,6 +11206,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11312,6 +11375,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11499,6 +11563,7 @@
           <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11670,6 +11735,7 @@
           <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Tom respire. Tom retient : manteau, sortir, rentrer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11865,6 +11931,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12032,6 +12099,7 @@
           <t>narrateur|Tom a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12227,6 +12295,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12394,6 +12463,7 @@
           <t>narrateur|Tom rejoint le matin. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12561,6 +12631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12728,6 +12799,7 @@
           <t>narrateur|Tom rejoint après la sieste. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12895,6 +12967,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13062,6 +13135,7 @@
           <t>narrateur|Tom rejoint le soir. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13229,6 +13303,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13396,6 +13471,7 @@
           <t>narrateur|Tom a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On montre du doigt, sans courir. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13591,6 +13667,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13758,6 +13835,7 @@
           <t>narrateur|Tom rejoint le matin. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13925,6 +14003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14092,6 +14171,7 @@
           <t>narrateur|Tom rejoint après la sieste. La lumière est claire. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14259,6 +14339,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14426,6 +14507,7 @@
           <t>narrateur|Tom rejoint le soir. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14593,6 +14675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14760,6 +14843,7 @@
           <t>narrateur|Tom a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On rit un peu. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14955,6 +15039,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15122,6 +15207,7 @@
           <t>narrateur|Tom rejoint le matin. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15289,6 +15375,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15456,6 +15543,7 @@
           <t>narrateur|Tom rejoint après la sieste. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15623,6 +15711,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15790,6 +15879,7 @@
           <t>narrateur|Tom rejoint le soir. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15957,6 +16047,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15975,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15999,6 +16090,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16200,6 +16305,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-027.xlsx
+++ b/stories/arbres/TREE-AUT-027.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prendre son manteau avant de sortir — au marché</t>
+          <t>Le manteau bleu de Mila au marché</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La bâche du marché claque. Mila prend le manteau bleu avant de sortir. Au retour, elle le raccroche.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Tom est avec papa, au marché. Tom a envie de jouer. papa est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom écoute papa. Tom entend les mots : manteau, sortir, rentrer.</t>
+          <t>La bâche du marché claque, tout loin. Elle est rayée, blanche et rouge. Une caisse d'oranges sent le soleil. Les pavés brillent encore un peu. Une flaque tient le ciel. Ça sent la menthe, et le pain chaud. Près de la porte, un crochet de bois attend. Un manteau bleu y pend, tout calme. Les boutons sont ronds et froids. Papa pose un panier d'osier. Le panier est encore vide. Le panier est prêt, Mila. Maman coupe une feuille de menthe. Tu as senti la menthe ? Oui, maman. En ce moment, Mila touche le manteau bleu. Je veux le marché ! D'accord. Avant de sortir, on prend le manteau. Pour rentrer, on le raccroche. Mila serre un bouton dans sa main.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,7 +1337,27 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Tom est avec papa, au marché. Tom a envie de jouer. papa est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom écoute papa. Tom entend les mots : manteau, sortir, rentrer.</t>
+          <t>narrateur|La bâche du marché claque, tout loin.
+narrateur|Elle est rayée, blanche et rouge.
+narrateur|Une caisse d'oranges sent le soleil.
+narrateur|Les pavés brillent encore un peu.
+narrateur|Une flaque tient le ciel.
+narrateur|Ça sent la menthe, et le pain chaud.
+narrateur|Près de la porte, un crochet de bois attend.
+narrateur|Un manteau bleu y pend, tout calme.
+narrateur|Les boutons sont ronds et froids.
+narrateur|Papa pose un panier d'osier.
+narrateur|Le panier est encore vide.
+papa|Le panier est prêt, Mila.
+narrateur|Maman coupe une feuille de menthe.
+maman|Tu as senti la menthe ?
+enfant-f|Oui, maman.
+narrateur|En ce moment, Mila touche le manteau bleu.
+enfant-f|Je veux le marché !
+papa|D'accord.
+papa|Avant de sortir, on prend le manteau.
+maman|Pour rentrer, on le raccroche.
+narrateur|Mila serre un bouton dans sa main.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1353,7 +1385,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>On peut aller dans la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1521,7 +1553,7 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>narrateur|On peut aller dans la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1549,7 +1581,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On dit merci. Je suis là. On reste ensemble.</t>
+          <t>Mila va vers la cuisine. Le carrelage est un peu froid. Le panier pose un cercle d'ombre. Une orange roule, tout doux. L'orange dans le panier, Mila. L'orange. Mila la pose. Ça sent le fruit. On sort au marché après. Avant de sortir, on prend le manteau. Mila court vers le crochet. Elle glisse un bras, puis l'autre. Le manteau bleu est chaud. Bravo. Tu as pris ton manteau. Papa ouvre la porte. L'air du marché entre, tout frais. Tu as les mains au chaud ? Oui. Dans les poches.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1689,8 +1721,26 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Tom va vers la cuisine. Les chaussures font toc toc. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On dit merci.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Mila va vers la cuisine.
+narrateur|Le carrelage est un peu froid.
+narrateur|Le panier pose un cercle d'ombre.
+narrateur|Une orange roule, tout doux.
+maman|L'orange dans le panier, Mila.
+enfant-f|L'orange.
+narrateur|Mila la pose.
+narrateur|Ça sent le fruit.
+papa|On sort au marché après.
+papa|Avant de sortir, on prend le manteau.
+narrateur|Mila court vers le crochet.
+narrateur|Elle glisse un bras, puis l'autre.
+narrateur|Le manteau bleu est chaud.
+maman|Bravo.
+maman|Tu as pris ton manteau.
+narrateur|Papa ouvre la porte.
+narrateur|L'air du marché entre, tout frais.
+papa|Tu as les mains au chaud ?
+enfant-f|Oui.
+enfant-f|Dans les poches.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1718,7 +1768,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>Avant de sortir, Mila prend quoi ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1878,7 +1928,7 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>narrateur|Avant de sortir, Mila prend quoi ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1906,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : prendre le manteau ; le raccrocher. Tom respire. Tom retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>Oui. On prend le manteau avant de sortir. Pour rentrer, on le raccroche. Le manteau bleu est fermé. Bravo, Mila. Tu as écouté. C'est du bon travail. J'ai mon manteau. On continue ensemble ? Oui.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2050,7 +2100,16 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Tom respire. Tom retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>narrateur|Oui.
+narrateur|On prend le manteau avant de sortir.
+narrateur|Pour rentrer, on le raccroche.
+narrateur|Le manteau bleu est fermé.
+maman|Bravo, Mila.
+maman|Tu as écouté.
+papa|C'est du bon travail.
+enfant-f|J'ai mon manteau.
+maman|On continue ensemble ?
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2274,7 +2333,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+          <t>Des cubes en bois attendent près du panier. Ils sentent le bois clair. Un cube dans le panier, Mila. Le cube. Mila le glisse près de l'orange. On sort. On prend le manteau. Mila a déjà le manteau bleu. Bravo. Tu l'as pris avant de sortir. Ils vont au marché. Le cube tapote contre l'osier. Quand on rentre, on raccroche. On raccroche.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2414,7 +2473,20 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+          <t>narrateur|Des cubes en bois attendent près du panier.
+narrateur|Ils sentent le bois clair.
+papa|Un cube dans le panier, Mila.
+enfant-f|Le cube.
+narrateur|Mila le glisse près de l'orange.
+maman|On sort.
+maman|On prend le manteau.
+narrateur|Mila a déjà le manteau bleu.
+papa|Bravo.
+papa|Tu l'as pris avant de sortir.
+narrateur|Ils vont au marché.
+narrateur|Le cube tapote contre l'osier.
+maman|Quand on rentre, on raccroche.
+enfant-f|On raccroche.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2442,7 +2514,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2610,7 +2682,7 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2638,7 +2710,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. Le sol est un peu froid. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le matin, l'air est tout frais. Une orange brille dans une caisse. Les pavés sont encore humides. C'est le matin. Le marché s'ouvre. On prend le manteau. Le cube tapote encore dans le panier. Ça sent encore la menthe, tout près. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai le cube. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la cuisine. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Il fait frais. Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2778,7 +2850,28 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. Le sol est un peu froid. On dit merci. Cette fin-là est celle de la cuisine, les cubes et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, l'air est tout frais.
+narrateur|Une orange brille dans une caisse.
+narrateur|Les pavés sont encore humides.
+enfant-f|C'est le matin.
+papa|Le marché s'ouvre.
+papa|On prend le manteau.
+narrateur|Le cube tapote encore dans le panier.
+narrateur|Ça sent encore la menthe, tout près.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai le cube.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la cuisine.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Il fait frais.
+maman|Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr"/>
@@ -2806,7 +2899,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une caisse d'oranges reste au stand. Mila raccroche le manteau bleu. Le cube reste dans le panier. Une miette d'orange reste sur le pouce. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2946,7 +3039,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Une caisse d'oranges reste au stand.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le cube reste dans le panier.
+narrateur|Une miette d'orange reste sur le pouce.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2974,7 +3076,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. Une feuille tombe. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les pavés sont chauds. Un store fait une ombre douce. Le marché est plus calme. Après la sieste. On ressort. On reprend le manteau. Le cube tapote encore dans le panier. Ça sent encore la menthe, tout près. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai le cube. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la cuisine. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Le soleil est là. Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3114,7 +3216,28 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. Une feuille tombe. On souffle doucement. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Un store fait une ombre douce.
+narrateur|Le marché est plus calme.
+enfant-f|Après la sieste.
+papa|On ressort.
+papa|On reprend le manteau.
+narrateur|Le cube tapote encore dans le panier.
+narrateur|Ça sent encore la menthe, tout près.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai le cube.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la cuisine.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Le soleil est là.
+maman|Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3142,7 +3265,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'ombre du store recule un peu. Mila raccroche le manteau bleu. Le cube reste dans le panier. Le bouton du manteau est encore froid. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3282,7 +3405,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'ombre du store recule un peu.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le cube reste dans le panier.
+narrateur|Le bouton du manteau est encore froid.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3310,7 +3442,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le soir, le ciel devient rose. Une lampe s'allume au stand. Les caisses s'empilent, tout doux. C'est le soir. On rentre bientôt. On raccroche après. Le cube tapote encore dans le panier. Ça sent encore la menthe, tout près. Ils rentrent. Le carrelage est froid. Mila a encore le manteau bleu. On rentre. On raccroche le manteau. J'ai le cube. Le crochet, Mila. Près de la cuisine. Mila raccroche le manteau bleu. Bravo. Tu as raccroché. Il commence à faire frais. On rentre. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3450,7 +3582,28 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, les cubes et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, le ciel devient rose.
+narrateur|Une lampe s'allume au stand.
+narrateur|Les caisses s'empilent, tout doux.
+enfant-f|C'est le soir.
+papa|On rentre bientôt.
+papa|On raccroche après.
+narrateur|Le cube tapote encore dans le panier.
+narrateur|Ça sent encore la menthe, tout près.
+narrateur|Ils rentrent.
+narrateur|Le carrelage est froid.
+narrateur|Mila a encore le manteau bleu.
+papa|On rentre.
+papa|On raccroche le manteau.
+enfant-f|J'ai le cube.
+maman|Le crochet, Mila.
+maman|Près de la cuisine.
+narrateur|Mila raccroche le manteau bleu.
+maman|Bravo.
+maman|Tu as raccroché.
+maman|Il commence à faire frais.
+maman|On rentre.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3478,7 +3631,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La lampe du stand s'éteint. Mila raccroche le manteau bleu. Le cube reste dans le panier. La flaque ne tient plus le ciel. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3618,7 +3771,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La lampe du stand s'éteint.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le cube reste dans le panier.
+narrateur|La flaque ne tient plus le ciel.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3646,7 +3808,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Un petit livre est sur la table. La couverture montre une poire. Le livre dans le panier, Mila. Le livre. Les pages sentent le papier. On va au marché. Le manteau d'abord. Mila touche le tissu bleu. Elle a déjà les manches. Bravo. Tu as pris ton manteau. Le panier est un peu lourd. Quand on rentre, on le raccroche. D'accord, papa.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3786,7 +3948,20 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>narrateur|Un petit livre est sur la table.
+narrateur|La couverture montre une poire.
+maman|Le livre dans le panier, Mila.
+enfant-f|Le livre.
+narrateur|Les pages sentent le papier.
+papa|On va au marché.
+papa|Le manteau d'abord.
+narrateur|Mila touche le tissu bleu.
+narrateur|Elle a déjà les manches.
+maman|Bravo.
+maman|Tu as pris ton manteau.
+narrateur|Le panier est un peu lourd.
+papa|Quand on rentre, on le raccroche.
+enfant-f|D'accord, papa.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3814,7 +3989,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3982,7 +4157,7 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4010,7 +4185,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. Une feuille tombe. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le matin, l'air est tout frais. Une orange brille dans une caisse. Les pavés sont encore humides. C'est le matin. Le marché s'ouvre. On prend le manteau. Le livre reste au fond, bien à plat. Ça sent encore la menthe, tout près. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai le livre. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la cuisine. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Il fait frais. Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4150,7 +4325,28 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. Une feuille tombe. On dit merci. Cette fin-là est celle de la cuisine, le livre et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, l'air est tout frais.
+narrateur|Une orange brille dans une caisse.
+narrateur|Les pavés sont encore humides.
+enfant-f|C'est le matin.
+papa|Le marché s'ouvre.
+papa|On prend le manteau.
+narrateur|Le livre reste au fond, bien à plat.
+narrateur|Ça sent encore la menthe, tout près.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai le livre.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la cuisine.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Il fait frais.
+maman|Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr"/>
@@ -4178,7 +4374,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une caisse d'oranges reste au stand. Mila raccroche le manteau bleu. Le livre reste dans le panier. La poire du livre est un peu pliée. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4318,7 +4514,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Une caisse d'oranges reste au stand.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le livre reste dans le panier.
+narrateur|La poire du livre est un peu pliée.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4346,7 +4551,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les pavés sont chauds. Un store fait une ombre douce. Le marché est plus calme. Après la sieste. On ressort. On reprend le manteau. Le livre reste au fond, bien à plat. Ça sent encore la menthe, tout près. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai le livre. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la cuisine. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Le soleil est là. Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4486,7 +4691,28 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de la cuisine, le livre et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Un store fait une ombre douce.
+narrateur|Le marché est plus calme.
+enfant-f|Après la sieste.
+papa|On ressort.
+papa|On reprend le manteau.
+narrateur|Le livre reste au fond, bien à plat.
+narrateur|Ça sent encore la menthe, tout près.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai le livre.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la cuisine.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Le soleil est là.
+maman|Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4514,7 +4740,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'ombre du store recule un peu. Mila raccroche le manteau bleu. Le livre reste dans le panier. Une feuille de menthe sèche sur la table. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4654,7 +4880,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'ombre du store recule un peu.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le livre reste dans le panier.
+narrateur|Une feuille de menthe sèche sur la table.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4682,7 +4917,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le soir, le ciel devient rose. Une lampe s'allume au stand. Les caisses s'empilent, tout doux. C'est le soir. On rentre bientôt. On raccroche après. Le livre reste au fond, bien à plat. Ça sent encore la menthe, tout près. Ils rentrent. Le carrelage est froid. Mila a encore le manteau bleu. On rentre. On raccroche le manteau. J'ai le livre. Le crochet, Mila. Près de la cuisine. Mila raccroche le manteau bleu. Bravo. Tu as raccroché. Il commence à faire frais. On rentre. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4822,7 +5057,28 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, le livre et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, le ciel devient rose.
+narrateur|Une lampe s'allume au stand.
+narrateur|Les caisses s'empilent, tout doux.
+enfant-f|C'est le soir.
+papa|On rentre bientôt.
+papa|On raccroche après.
+narrateur|Le livre reste au fond, bien à plat.
+narrateur|Ça sent encore la menthe, tout près.
+narrateur|Ils rentrent.
+narrateur|Le carrelage est froid.
+narrateur|Mila a encore le manteau bleu.
+papa|On rentre.
+papa|On raccroche le manteau.
+enfant-f|J'ai le livre.
+maman|Le crochet, Mila.
+maman|Près de la cuisine.
+narrateur|Mila raccroche le manteau bleu.
+maman|Bravo.
+maman|Tu as raccroché.
+maman|Il commence à faire frais.
+maman|On rentre.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4850,7 +5106,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La lampe du stand s'éteint. Mila raccroche le manteau bleu. Le livre reste dans le panier. Le panier d'osier sent le pain. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4990,7 +5246,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La lampe du stand s'éteint.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le livre reste dans le panier.
+narrateur|Le panier d'osier sent le pain.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5018,7 +5283,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On rit un peu. maman n'est pas loin.</t>
+          <t>Une tasse de dînette brille près de l'évier. Elle est jaune et légère. La petite tasse, Mila. La tasse. Mila la pose dans le panier. Comme au marché. On vend des choses. Avant de sortir, le manteau. Le manteau bleu est déjà sur Mila. Bravo. Tu l'as pris. La tasse tinte contre l'orange. En rentrant, on raccroche le manteau. On raccroche.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5158,7 +5423,20 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On rit un peu. maman n'est pas loin.</t>
+          <t>narrateur|Une tasse de dînette brille près de l'évier.
+narrateur|Elle est jaune et légère.
+papa|La petite tasse, Mila.
+enfant-f|La tasse.
+narrateur|Mila la pose dans le panier.
+maman|Comme au marché.
+maman|On vend des choses.
+papa|Avant de sortir, le manteau.
+narrateur|Le manteau bleu est déjà sur Mila.
+maman|Bravo.
+maman|Tu l'as pris.
+narrateur|La tasse tinte contre l'orange.
+papa|En rentrant, on raccroche le manteau.
+enfant-f|On raccroche.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5186,7 +5464,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5354,7 +5632,7 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5382,7 +5660,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le matin, l'air est tout frais. Une orange brille dans une caisse. Les pavés sont encore humides. C'est le matin. Le marché s'ouvre. On prend le manteau. La petite tasse tinte, tout doux. Ça sent encore la menthe, tout près. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai la tasse. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la cuisine. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Il fait frais. Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5522,7 +5800,28 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. L'eau coule, tout petit bruit. On dit merci. Cette fin-là est celle de la cuisine, la dînette et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, l'air est tout frais.
+narrateur|Une orange brille dans une caisse.
+narrateur|Les pavés sont encore humides.
+enfant-f|C'est le matin.
+papa|Le marché s'ouvre.
+papa|On prend le manteau.
+narrateur|La petite tasse tinte, tout doux.
+narrateur|Ça sent encore la menthe, tout près.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai la tasse.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la cuisine.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Il fait frais.
+maman|Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr"/>
@@ -5550,7 +5849,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une caisse d'oranges reste au stand. Mila raccroche le manteau bleu. La dînette reste dans le panier. La tasse jaune ne tinte plus. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5690,7 +5989,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Une caisse d'oranges reste au stand.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|La dînette reste dans le panier.
+narrateur|La tasse jaune ne tinte plus.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5718,7 +6026,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les pavés sont chauds. Un store fait une ombre douce. Le marché est plus calme. Après la sieste. On ressort. On reprend le manteau. La petite tasse tinte, tout doux. Ça sent encore la menthe, tout près. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai la tasse. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la cuisine. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Le soleil est là. Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5858,7 +6166,28 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Un store fait une ombre douce.
+narrateur|Le marché est plus calme.
+enfant-f|Après la sieste.
+papa|On ressort.
+papa|On reprend le manteau.
+narrateur|La petite tasse tinte, tout doux.
+narrateur|Ça sent encore la menthe, tout près.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai la tasse.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la cuisine.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Le soleil est là.
+maman|Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5886,7 +6215,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'ombre du store recule un peu. Mila raccroche le manteau bleu. La dînette reste dans le panier. Le carrelage n'est plus si froid. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6026,7 +6355,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'ombre du store recule un peu.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|La dînette reste dans le panier.
+narrateur|Le carrelage n'est plus si froid.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6054,7 +6392,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le soir, le ciel devient rose. Une lampe s'allume au stand. Les caisses s'empilent, tout doux. C'est le soir. On rentre bientôt. On raccroche après. La petite tasse tinte, tout doux. Ça sent encore la menthe, tout près. Ils rentrent. Le carrelage est froid. Mila a encore le manteau bleu. On rentre. On raccroche le manteau. J'ai la tasse. Le crochet, Mila. Près de la cuisine. Mila raccroche le manteau bleu. Bravo. Tu as raccroché. Il commence à faire frais. On rentre. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6194,7 +6532,28 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la cuisine, la dînette et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, le ciel devient rose.
+narrateur|Une lampe s'allume au stand.
+narrateur|Les caisses s'empilent, tout doux.
+enfant-f|C'est le soir.
+papa|On rentre bientôt.
+papa|On raccroche après.
+narrateur|La petite tasse tinte, tout doux.
+narrateur|Ça sent encore la menthe, tout près.
+narrateur|Ils rentrent.
+narrateur|Le carrelage est froid.
+narrateur|Mila a encore le manteau bleu.
+papa|On rentre.
+papa|On raccroche le manteau.
+enfant-f|J'ai la tasse.
+maman|Le crochet, Mila.
+maman|Près de la cuisine.
+narrateur|Mila raccroche le manteau bleu.
+maman|Bravo.
+maman|Tu as raccroché.
+maman|Il commence à faire frais.
+maman|On rentre.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6222,7 +6581,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La lampe du stand s'éteint. Mila raccroche le manteau bleu. La dînette reste dans le panier. Une caisse se ferme, tout loin. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6362,7 +6721,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La lampe du stand s'éteint.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|La dînette reste dans le panier.
+narrateur|Une caisse se ferme, tout loin.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6390,7 +6758,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On souffle doucement. Je suis là. On reste ensemble.</t>
+          <t>Mila va vers le jardin. L'herbe est encore un peu mouillée. Une feuille colle à sa chaussure. On passe par le jardin, Mila. Ensuite le marché. Les pavés brillent. Oui. Ils sont encore frais. Avant de sortir, on prend le manteau. Mila revient vers le crochet. Elle enfile le manteau bleu. Bravo. Tu as pris ton manteau. Ils marchent dans l'herbe. Le panier frotte un peu la hanche. Quand on rentre, on le raccroche. Oui, maman.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6530,8 +6898,23 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Tom va vers le jardin. La couverture est douce. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On souffle doucement.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Mila va vers le jardin.
+narrateur|L'herbe est encore un peu mouillée.
+narrateur|Une feuille colle à sa chaussure.
+papa|On passe par le jardin, Mila.
+papa|Ensuite le marché.
+enfant-f|Les pavés brillent.
+maman|Oui.
+maman|Ils sont encore frais.
+maman|Avant de sortir, on prend le manteau.
+narrateur|Mila revient vers le crochet.
+narrateur|Elle enfile le manteau bleu.
+papa|Bravo.
+papa|Tu as pris ton manteau.
+narrateur|Ils marchent dans l'herbe.
+narrateur|Le panier frotte un peu la hanche.
+maman|Quand on rentre, on le raccroche.
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6559,7 +6942,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>On prend quoi, avant de sortir ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6719,7 +7102,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>narrateur|On prend quoi, avant de sortir ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6747,7 +7130,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : prendre le manteau ; le raccrocher. Tom respire. Tom retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>Oui. On prend le manteau avant de sortir. Pour rentrer, on le raccroche. Bravo, Mila. Tu as fait du bon travail. Le manteau bleu te tient chaud. Il est chaud. On continue ? Oui.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6891,7 +7274,15 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Tom respire. Tom retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>narrateur|Oui.
+narrateur|On prend le manteau avant de sortir.
+narrateur|Pour rentrer, on le raccroche.
+papa|Bravo, Mila.
+papa|Tu as fait du bon travail.
+maman|Le manteau bleu te tient chaud.
+enfant-f|Il est chaud.
+papa|On continue ?
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -7115,7 +7506,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+          <t>Des cubes sont dans l'herbe, près du muret. Un cube vert est un peu humide. Les cubes secs, Mila. Les cubes secs. Mila en prend deux. Elle les met dans le panier. Tu as ton manteau, hein ? Oui. Le bleu. Bravo. Tu l'as pris avant de sortir. Un oiseau passe tout bas. Quand on rentre, on raccroche. On raccroche.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7255,7 +7646,20 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi les cubes. Le sol est un peu froid. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+          <t>narrateur|Des cubes sont dans l'herbe, près du muret.
+narrateur|Un cube vert est un peu humide.
+maman|Les cubes secs, Mila.
+enfant-f|Les cubes secs.
+narrateur|Mila en prend deux.
+narrateur|Elle les met dans le panier.
+papa|Tu as ton manteau, hein ?
+enfant-f|Oui.
+enfant-f|Le bleu.
+maman|Bravo.
+maman|Tu l'as pris avant de sortir.
+narrateur|Un oiseau passe tout bas.
+papa|Quand on rentre, on raccroche.
+enfant-f|On raccroche.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7283,7 +7687,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7451,7 +7855,7 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7479,7 +7883,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le matin, l'air est tout frais. Une orange brille dans une caisse. Les pavés sont encore humides. C'est le matin. Le marché s'ouvre. On prend le manteau. Le cube tapote encore dans le panier. Une goutte tombe d'une feuille. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai le cube. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la porte. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Il fait frais. Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7619,7 +8023,28 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. Une feuille tombe. On souffle doucement. Cette fin-là est celle de le jardin, les cubes et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, l'air est tout frais.
+narrateur|Une orange brille dans une caisse.
+narrateur|Les pavés sont encore humides.
+enfant-f|C'est le matin.
+papa|Le marché s'ouvre.
+papa|On prend le manteau.
+narrateur|Le cube tapote encore dans le panier.
+narrateur|Une goutte tombe d'une feuille.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai le cube.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la porte.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Il fait frais.
+maman|Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr"/>
@@ -7647,7 +8072,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une caisse d'oranges reste au stand. Mila raccroche le manteau bleu. Le cube reste dans le panier. Une goutte tombe d'une feuille. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7787,7 +8212,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Une caisse d'oranges reste au stand.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le cube reste dans le panier.
+narrateur|Une goutte tombe d'une feuille.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7815,7 +8249,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les pavés sont chauds. Un store fait une ombre douce. Le marché est plus calme. Après la sieste. On ressort. On reprend le manteau. Le cube tapote encore dans le panier. Une goutte tombe d'une feuille. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai le cube. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la porte. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Le soleil est là. Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7955,7 +8389,28 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, les cubes et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Un store fait une ombre douce.
+narrateur|Le marché est plus calme.
+enfant-f|Après la sieste.
+papa|On ressort.
+papa|On reprend le manteau.
+narrateur|Le cube tapote encore dans le panier.
+narrateur|Une goutte tombe d'une feuille.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai le cube.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la porte.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Le soleil est là.
+maman|Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7983,7 +8438,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'ombre du store recule un peu. Mila raccroche le manteau bleu. Le cube reste dans le panier. Le muret est encore chaud. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8123,7 +8578,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'ombre du store recule un peu.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le cube reste dans le panier.
+narrateur|Le muret est encore chaud.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8151,7 +8615,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le soir, le ciel devient rose. Une lampe s'allume au stand. Les caisses s'empilent, tout doux. C'est le soir. On rentre bientôt. On raccroche après. Le cube tapote encore dans le panier. Une goutte tombe d'une feuille. Ils rentrent par l'herbe. Elle est froide. Mila a encore le manteau bleu. On rentre. On raccroche le manteau. J'ai le cube. Le crochet, Mila. Près de la porte. Mila raccroche le manteau bleu. Bravo. Tu as raccroché. Il commence à faire frais. On rentre. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8291,7 +8755,28 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de le jardin, les cubes et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, le ciel devient rose.
+narrateur|Une lampe s'allume au stand.
+narrateur|Les caisses s'empilent, tout doux.
+enfant-f|C'est le soir.
+papa|On rentre bientôt.
+papa|On raccroche après.
+narrateur|Le cube tapote encore dans le panier.
+narrateur|Une goutte tombe d'une feuille.
+narrateur|Ils rentrent par l'herbe.
+narrateur|Elle est froide.
+narrateur|Mila a encore le manteau bleu.
+papa|On rentre.
+papa|On raccroche le manteau.
+enfant-f|J'ai le cube.
+maman|Le crochet, Mila.
+maman|Près de la porte.
+narrateur|Mila raccroche le manteau bleu.
+maman|Bravo.
+maman|Tu as raccroché.
+maman|Il commence à faire frais.
+maman|On rentre.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8319,7 +8804,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La lampe du stand s'éteint. Mila raccroche le manteau bleu. Le cube reste dans le panier. L'oiseau n'est plus là. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8459,7 +8944,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La lampe du stand s'éteint.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le cube reste dans le panier.
+narrateur|L'oiseau n'est plus là.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8487,7 +8981,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Le livre est sur le muret, au soleil. La couverture est un peu chaude. Le livre dans le panier, Mila. Le livre. Mila le souffle, puis le pose. Tu as pris ton manteau. Le tissu bleu frotte le panier. Bravo. C'est du bon travail. Une fourmi passe sur la pierre. On laisse la fourmi. En rentrant, on raccroche le manteau. Oui, papa.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8627,7 +9121,19 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi le livre. Une feuille tombe. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>narrateur|Le livre est sur le muret, au soleil.
+narrateur|La couverture est un peu chaude.
+papa|Le livre dans le panier, Mila.
+enfant-f|Le livre.
+narrateur|Mila le souffle, puis le pose.
+maman|Tu as pris ton manteau.
+narrateur|Le tissu bleu frotte le panier.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Une fourmi passe sur la pierre.
+maman|On laisse la fourmi.
+papa|En rentrant, on raccroche le manteau.
+enfant-f|Oui, papa.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8655,7 +9161,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8823,7 +9329,7 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8851,7 +9357,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le matin, l'air est tout frais. Une orange brille dans une caisse. Les pavés sont encore humides. C'est le matin. Le marché s'ouvre. On prend le manteau. Le livre reste au fond, bien à plat. Une goutte tombe d'une feuille. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai le livre. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la porte. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Il fait frais. Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8991,7 +9497,28 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. L'eau coule, tout petit bruit. On souffle doucement. Cette fin-là est celle de le jardin, le livre et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, l'air est tout frais.
+narrateur|Une orange brille dans une caisse.
+narrateur|Les pavés sont encore humides.
+enfant-f|C'est le matin.
+papa|Le marché s'ouvre.
+papa|On prend le manteau.
+narrateur|Le livre reste au fond, bien à plat.
+narrateur|Une goutte tombe d'une feuille.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai le livre.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la porte.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Il fait frais.
+maman|Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr"/>
@@ -9019,7 +9546,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une caisse d'oranges reste au stand. Mila raccroche le manteau bleu. Le livre reste dans le panier. La fourmi a quitté la pierre. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9159,7 +9686,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Une caisse d'oranges reste au stand.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le livre reste dans le panier.
+narrateur|La fourmi a quitté la pierre.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9187,7 +9723,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les pavés sont chauds. Un store fait une ombre douce. Le marché est plus calme. Après la sieste. On ressort. On reprend le manteau. Le livre reste au fond, bien à plat. Une goutte tombe d'une feuille. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai le livre. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la porte. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Le soleil est là. Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9327,7 +9863,28 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, le livre et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Un store fait une ombre douce.
+narrateur|Le marché est plus calme.
+enfant-f|Après la sieste.
+papa|On ressort.
+papa|On reprend le manteau.
+narrateur|Le livre reste au fond, bien à plat.
+narrateur|Une goutte tombe d'une feuille.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai le livre.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la porte.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Le soleil est là.
+maman|Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9355,7 +9912,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'ombre du store recule un peu. Mila raccroche le manteau bleu. Le livre reste dans le panier. L'herbe colle encore à la chaussure. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9495,7 +10052,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'ombre du store recule un peu.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le livre reste dans le panier.
+narrateur|L'herbe colle encore à la chaussure.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9523,7 +10089,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. La lumière est claire. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le soir, le ciel devient rose. Une lampe s'allume au stand. Les caisses s'empilent, tout doux. C'est le soir. On rentre bientôt. On raccroche après. Le livre reste au fond, bien à plat. Une goutte tombe d'une feuille. Ils rentrent par l'herbe. Elle est froide. Mila a encore le manteau bleu. On rentre. On raccroche le manteau. J'ai le livre. Le crochet, Mila. Près de la porte. Mila raccroche le manteau bleu. Bravo. Tu as raccroché. Il commence à faire frais. On rentre. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9663,7 +10229,28 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. La lumière est claire. On attend son tour. Cette fin-là est celle de le jardin, le livre et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, le ciel devient rose.
+narrateur|Une lampe s'allume au stand.
+narrateur|Les caisses s'empilent, tout doux.
+enfant-f|C'est le soir.
+papa|On rentre bientôt.
+papa|On raccroche après.
+narrateur|Le livre reste au fond, bien à plat.
+narrateur|Une goutte tombe d'une feuille.
+narrateur|Ils rentrent par l'herbe.
+narrateur|Elle est froide.
+narrateur|Mila a encore le manteau bleu.
+papa|On rentre.
+papa|On raccroche le manteau.
+enfant-f|J'ai le livre.
+maman|Le crochet, Mila.
+maman|Près de la porte.
+narrateur|Mila raccroche le manteau bleu.
+maman|Bravo.
+maman|Tu as raccroché.
+maman|Il commence à faire frais.
+maman|On rentre.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9691,7 +10278,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La lampe du stand s'éteint. Mila raccroche le manteau bleu. Le livre reste dans le panier. Le store s'est un peu relevé. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9831,7 +10418,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La lampe du stand s'éteint.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le livre reste dans le panier.
+narrateur|Le store s'est un peu relevé.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9859,7 +10455,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On rit un peu. maman n'est pas loin.</t>
+          <t>Une cuillère de dînette brille dans l'herbe. Elle est petite et froide. La petite cuillère, Mila. La cuillère. Mila la glisse dans le panier. Comme au stand. On range les outils. Tu as le manteau, Mila ? Oui. Il est bleu. Bravo. Tu l'as pris pour sortir. La cuillère tinte tout doux. Quand on rentre, on le raccroche. On le raccroche.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9999,7 +10595,21 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi la dînette. L'eau coule, tout petit bruit. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On rit un peu. maman n'est pas loin.</t>
+          <t>narrateur|Une cuillère de dînette brille dans l'herbe.
+narrateur|Elle est petite et froide.
+maman|La petite cuillère, Mila.
+enfant-f|La cuillère.
+narrateur|Mila la glisse dans le panier.
+papa|Comme au stand.
+papa|On range les outils.
+maman|Tu as le manteau, Mila ?
+enfant-f|Oui.
+enfant-f|Il est bleu.
+papa|Bravo.
+papa|Tu l'as pris pour sortir.
+narrateur|La cuillère tinte tout doux.
+maman|Quand on rentre, on le raccroche.
+enfant-f|On le raccroche.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -10027,7 +10637,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10195,7 +10805,7 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10223,7 +10833,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le matin, l'air est tout frais. Une orange brille dans une caisse. Les pavés sont encore humides. C'est le matin. Le marché s'ouvre. On prend le manteau. La petite tasse tinte, tout doux. Une goutte tombe d'une feuille. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai la tasse. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la porte. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Il fait frais. Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10363,7 +10973,28 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. Un vélo passe au loin. On souffle doucement. Cette fin-là est celle de le jardin, la dînette et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, l'air est tout frais.
+narrateur|Une orange brille dans une caisse.
+narrateur|Les pavés sont encore humides.
+enfant-f|C'est le matin.
+papa|Le marché s'ouvre.
+papa|On prend le manteau.
+narrateur|La petite tasse tinte, tout doux.
+narrateur|Une goutte tombe d'une feuille.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai la tasse.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la porte.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Il fait frais.
+maman|Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr"/>
@@ -10391,7 +11022,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une caisse d'oranges reste au stand. Mila raccroche le manteau bleu. La dînette reste dans le panier. La cuillère de dînette est sèche. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10531,7 +11162,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Une caisse d'oranges reste au stand.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|La dînette reste dans le panier.
+narrateur|La cuillère de dînette est sèche.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10559,7 +11199,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les pavés sont chauds. Un store fait une ombre douce. Le marché est plus calme. Après la sieste. On ressort. On reprend le manteau. La petite tasse tinte, tout doux. Une goutte tombe d'une feuille. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai la tasse. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la porte. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Le soleil est là. Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10699,7 +11339,28 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de le jardin, la dînette et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Un store fait une ombre douce.
+narrateur|Le marché est plus calme.
+enfant-f|Après la sieste.
+papa|On ressort.
+papa|On reprend le manteau.
+narrateur|La petite tasse tinte, tout doux.
+narrateur|Une goutte tombe d'une feuille.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai la tasse.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la porte.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Le soleil est là.
+maman|Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10727,7 +11388,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'ombre du store recule un peu. Mila raccroche le manteau bleu. La dînette reste dans le panier. Le jardin sent la terre. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10867,7 +11528,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'ombre du store recule un peu.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|La dînette reste dans le panier.
+narrateur|Le jardin sent la terre.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10895,7 +11565,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le soir, le ciel devient rose. Une lampe s'allume au stand. Les caisses s'empilent, tout doux. C'est le soir. On rentre bientôt. On raccroche après. La petite tasse tinte, tout doux. Une goutte tombe d'une feuille. Ils rentrent par l'herbe. Elle est froide. Mila a encore le manteau bleu. On rentre. On raccroche le manteau. J'ai la tasse. Le crochet, Mila. Près de la porte. Mila raccroche le manteau bleu. Bravo. Tu as raccroché. Il commence à faire frais. On rentre. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11035,7 +11705,28 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de le jardin, la dînette et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, le ciel devient rose.
+narrateur|Une lampe s'allume au stand.
+narrateur|Les caisses s'empilent, tout doux.
+enfant-f|C'est le soir.
+papa|On rentre bientôt.
+papa|On raccroche après.
+narrateur|La petite tasse tinte, tout doux.
+narrateur|Une goutte tombe d'une feuille.
+narrateur|Ils rentrent par l'herbe.
+narrateur|Elle est froide.
+narrateur|Mila a encore le manteau bleu.
+papa|On rentre.
+papa|On raccroche le manteau.
+enfant-f|J'ai la tasse.
+maman|Le crochet, Mila.
+maman|Près de la porte.
+narrateur|Mila raccroche le manteau bleu.
+maman|Bravo.
+maman|Tu as raccroché.
+maman|Il commence à faire frais.
+maman|On rentre.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11063,7 +11754,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La lampe du stand s'éteint. Mila raccroche le manteau bleu. La dînette reste dans le panier. Un vélo passe, tout loin. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11203,7 +11894,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La lampe du stand s'éteint.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|La dînette reste dans le panier.
+narrateur|Un vélo passe, tout loin.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11231,7 +11931,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Tom va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On écoute jusqu'au bout. Je suis là. On reste ensemble.</t>
+          <t>Mila va vers la chambre. Le rideau est un peu ouvert. La bâche du marché se voit, tout loin. Tu as vu la bâche, Mila ? Elle claque. On va y aller. D'abord le manteau. Le manteau bleu est sur la chaise. Mila le prend à deux mains. Elle glisse les manches. Bravo. Tu as pris ton manteau. Un rayon touche le plancher. Quand on rentre, on le raccroche. Au crochet. Oui. Au crochet de bois.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11371,8 +12071,23 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Tom va vers la chambre. On entend un oiseau. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Tom se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On écoute jusqu'au bout.
-papa|Je suis là. On reste ensemble.</t>
+          <t>narrateur|Mila va vers la chambre.
+narrateur|Le rideau est un peu ouvert.
+narrateur|La bâche du marché se voit, tout loin.
+maman|Tu as vu la bâche, Mila ?
+enfant-f|Elle claque.
+papa|On va y aller.
+papa|D'abord le manteau.
+narrateur|Le manteau bleu est sur la chaise.
+narrateur|Mila le prend à deux mains.
+narrateur|Elle glisse les manches.
+maman|Bravo.
+maman|Tu as pris ton manteau.
+narrateur|Un rayon touche le plancher.
+papa|Quand on rentre, on le raccroche.
+enfant-f|Au crochet.
+maman|Oui.
+maman|Au crochet de bois.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11400,7 +12115,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>Quand on rentre, on raccroche quoi ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11560,7 +12275,7 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>narrateur|Quand on rentre, on raccroche quoi ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11588,7 +12303,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : prendre le manteau ; le raccrocher. Tom respire. Tom retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>Oui. On raccroche le manteau pour rentrer. On le prend avant de sortir. Bravo, Mila. Tu as écouté. Le crochet attend près de la porte. Je le saurai. On continue ensemble ? Oui.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11732,7 +12447,15 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Tom respire. Tom retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>narrateur|Oui.
+narrateur|On raccroche le manteau pour rentrer.
+narrateur|On le prend avant de sortir.
+maman|Bravo, Mila.
+maman|Tu as écouté.
+papa|Le crochet attend près de la porte.
+enfant-f|Je le saurai.
+maman|On continue ensemble ?
+enfant-f|Oui.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11956,7 +12679,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+          <t>Des cubes sont sous le lit. Un cube rouge roule, tout doux. Le cube rouge, Mila. Le cube. Mila le met dans le panier. Tu as le manteau, déjà. Le capuchon bleu touche son dos. Bravo. Tu l'as pris avant de sortir. Le cube tape le fond d'osier. Quand on rentre, on raccroche. Au crochet. Oui. Au crochet.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12096,7 +12819,20 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On attend son tour. maman n'est pas loin.</t>
+          <t>narrateur|Des cubes sont sous le lit.
+narrateur|Un cube rouge roule, tout doux.
+papa|Le cube rouge, Mila.
+enfant-f|Le cube.
+narrateur|Mila le met dans le panier.
+maman|Tu as le manteau, déjà.
+narrateur|Le capuchon bleu touche son dos.
+papa|Bravo.
+papa|Tu l'as pris avant de sortir.
+narrateur|Le cube tape le fond d'osier.
+maman|Quand on rentre, on raccroche.
+enfant-f|Au crochet.
+papa|Oui.
+papa|Au crochet.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12124,7 +12860,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12292,7 +13028,7 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12320,7 +13056,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le matin, l'air est tout frais. Une orange brille dans une caisse. Les pavés sont encore humides. C'est le matin. Le marché s'ouvre. On prend le manteau. Le cube tapote encore dans le panier. Le rideau bouge. La bâche claque, tout loin. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai le cube. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la chaise. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Il fait frais. Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12460,7 +13196,29 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. L'eau coule, tout petit bruit. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, les cubes et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, l'air est tout frais.
+narrateur|Une orange brille dans une caisse.
+narrateur|Les pavés sont encore humides.
+enfant-f|C'est le matin.
+papa|Le marché s'ouvre.
+papa|On prend le manteau.
+narrateur|Le cube tapote encore dans le panier.
+narrateur|Le rideau bouge.
+narrateur|La bâche claque, tout loin.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai le cube.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la chaise.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Il fait frais.
+maman|Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr"/>
@@ -12488,7 +13246,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une caisse d'oranges reste au stand. Mila raccroche le manteau bleu. Le cube reste dans le panier. Le rideau ne bouge plus. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12628,7 +13386,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Une caisse d'oranges reste au stand.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le cube reste dans le panier.
+narrateur|Le rideau ne bouge plus.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12656,7 +13423,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les pavés sont chauds. Un store fait une ombre douce. Le marché est plus calme. Après la sieste. On ressort. On reprend le manteau. Le cube tapote encore dans le panier. Le rideau bouge. La bâche claque, tout loin. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai le cube. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la chaise. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Le soleil est là. Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12796,7 +13563,29 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. Un vélo passe au loin. On attend son tour. Cette fin-là est celle de la chambre, les cubes et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Un store fait une ombre douce.
+narrateur|Le marché est plus calme.
+enfant-f|Après la sieste.
+papa|On ressort.
+papa|On reprend le manteau.
+narrateur|Le cube tapote encore dans le panier.
+narrateur|Le rideau bouge.
+narrateur|La bâche claque, tout loin.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai le cube.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la chaise.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Le soleil est là.
+maman|Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12824,7 +13613,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'ombre du store recule un peu. Mila raccroche le manteau bleu. Le cube reste dans le panier. Le plancher a perdu son rayon. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12964,7 +13753,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'ombre du store recule un peu.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le cube reste dans le panier.
+narrateur|Le plancher a perdu son rayon.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12992,7 +13790,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le soir, le ciel devient rose. Une lampe s'allume au stand. Les caisses s'empilent, tout doux. C'est le soir. On rentre bientôt. On raccroche après. Le cube tapote encore dans le panier. Le rideau bouge. La bâche claque, tout loin. Ils rentrent. La chambre est calme. Mila a encore le manteau bleu. On rentre. On raccroche le manteau. J'ai le cube. Le crochet, Mila. Près de la chaise. Mila raccroche le manteau bleu. Bravo. Tu as raccroché. Il commence à faire frais. On rentre. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13132,7 +13930,29 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. La lumière est claire. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, les cubes et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, le ciel devient rose.
+narrateur|Une lampe s'allume au stand.
+narrateur|Les caisses s'empilent, tout doux.
+enfant-f|C'est le soir.
+papa|On rentre bientôt.
+papa|On raccroche après.
+narrateur|Le cube tapote encore dans le panier.
+narrateur|Le rideau bouge.
+narrateur|La bâche claque, tout loin.
+narrateur|Ils rentrent.
+narrateur|La chambre est calme.
+narrateur|Mila a encore le manteau bleu.
+papa|On rentre.
+papa|On raccroche le manteau.
+enfant-f|J'ai le cube.
+maman|Le crochet, Mila.
+maman|Près de la chaise.
+narrateur|Mila raccroche le manteau bleu.
+maman|Bravo.
+maman|Tu as raccroché.
+maman|Il commence à faire frais.
+maman|On rentre.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13160,7 +13980,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La lampe du stand s'éteint. Mila raccroche le manteau bleu. Le cube reste dans le panier. La bâche ne claque plus. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13300,7 +14120,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La lampe du stand s'éteint.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le cube reste dans le panier.
+narrateur|La bâche ne claque plus.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13328,7 +14157,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>Le livre est sur l'oreiller. Il est encore un peu chaud. Le livre dans le panier, Mila. Le livre. Mila le glisse près de l'orange. On va au marché. Le manteau est déjà pris. Bravo. Tu as pris ton manteau. Le rideau bouge un peu. La bâche claque encore. Quand on rentre, on raccroche. Le crochet attend.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13468,7 +14297,19 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On montre du doigt, sans courir. maman n'est pas loin.</t>
+          <t>narrateur|Le livre est sur l'oreiller.
+narrateur|Il est encore un peu chaud.
+maman|Le livre dans le panier, Mila.
+enfant-f|Le livre.
+narrateur|Mila le glisse près de l'orange.
+papa|On va au marché.
+papa|Le manteau est déjà pris.
+maman|Bravo.
+maman|Tu as pris ton manteau.
+narrateur|Le rideau bouge un peu.
+enfant-f|La bâche claque encore.
+maman|Quand on rentre, on raccroche.
+papa|Le crochet attend.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13496,7 +14337,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13664,7 +14505,7 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13692,7 +14533,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le matin, l'air est tout frais. Une orange brille dans une caisse. Les pavés sont encore humides. C'est le matin. Le marché s'ouvre. On prend le manteau. Le livre reste au fond, bien à plat. Le rideau bouge. La bâche claque, tout loin. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai le livre. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la chaise. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Il fait frais. Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13832,7 +14673,29 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. Un vélo passe au loin. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, le livre et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, l'air est tout frais.
+narrateur|Une orange brille dans une caisse.
+narrateur|Les pavés sont encore humides.
+enfant-f|C'est le matin.
+papa|Le marché s'ouvre.
+papa|On prend le manteau.
+narrateur|Le livre reste au fond, bien à plat.
+narrateur|Le rideau bouge.
+narrateur|La bâche claque, tout loin.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai le livre.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la chaise.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Il fait frais.
+maman|Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr"/>
@@ -13860,7 +14723,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une caisse d'oranges reste au stand. Mila raccroche le manteau bleu. Le livre reste dans le panier. L'oreiller est encore creux. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14000,7 +14863,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Une caisse d'oranges reste au stand.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le livre reste dans le panier.
+narrateur|L'oreiller est encore creux.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14028,7 +14900,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. La lumière est claire. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les pavés sont chauds. Un store fait une ombre douce. Le marché est plus calme. Après la sieste. On ressort. On reprend le manteau. Le livre reste au fond, bien à plat. Le rideau bouge. La bâche claque, tout loin. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai le livre. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la chaise. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Le soleil est là. Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14168,7 +15040,29 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. La lumière est claire. On attend son tour. Cette fin-là est celle de la chambre, le livre et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Un store fait une ombre douce.
+narrateur|Le marché est plus calme.
+enfant-f|Après la sieste.
+papa|On ressort.
+papa|On reprend le manteau.
+narrateur|Le livre reste au fond, bien à plat.
+narrateur|Le rideau bouge.
+narrateur|La bâche claque, tout loin.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai le livre.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la chaise.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Le soleil est là.
+maman|Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14196,7 +15090,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'ombre du store recule un peu. Mila raccroche le manteau bleu. Le livre reste dans le panier. La chaise est vide, près du lit. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14336,7 +15230,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'ombre du store recule un peu.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le livre reste dans le panier.
+narrateur|La chaise est vide, près du lit.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14364,7 +15267,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le soir, le ciel devient rose. Une lampe s'allume au stand. Les caisses s'empilent, tout doux. C'est le soir. On rentre bientôt. On raccroche après. Le livre reste au fond, bien à plat. Le rideau bouge. La bâche claque, tout loin. Ils rentrent. La chambre est calme. Mila a encore le manteau bleu. On rentre. On raccroche le manteau. J'ai le livre. Le crochet, Mila. Près de la chaise. Mila raccroche le manteau bleu. Bravo. Tu as raccroché. Il commence à faire frais. On rentre. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14504,7 +15407,29 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. Il y a des miettes sur la table. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, le livre et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, le ciel devient rose.
+narrateur|Une lampe s'allume au stand.
+narrateur|Les caisses s'empilent, tout doux.
+enfant-f|C'est le soir.
+papa|On rentre bientôt.
+papa|On raccroche après.
+narrateur|Le livre reste au fond, bien à plat.
+narrateur|Le rideau bouge.
+narrateur|La bâche claque, tout loin.
+narrateur|Ils rentrent.
+narrateur|La chambre est calme.
+narrateur|Mila a encore le manteau bleu.
+papa|On rentre.
+papa|On raccroche le manteau.
+enfant-f|J'ai le livre.
+maman|Le crochet, Mila.
+maman|Près de la chaise.
+narrateur|Mila raccroche le manteau bleu.
+maman|Bravo.
+maman|Tu as raccroché.
+maman|Il commence à faire frais.
+maman|On rentre.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14532,7 +15457,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La lampe du stand s'éteint. Mila raccroche le manteau bleu. Le livre reste dans le panier. Un grain de poussière tourne. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14672,7 +15597,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La lampe du stand s'éteint.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|Le livre reste dans le panier.
+narrateur|Un grain de poussière tourne.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14700,7 +15634,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Tom a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On rit un peu. maman n'est pas loin.</t>
+          <t>Une assiette de dînette attend sur la commode. Elle est rose et légère. La petite assiette, Mila. L'assiette. Mila la pose dans le panier. On fera un stand, tout petit. Le manteau bleu est fermé. Bravo. Tu l'as pris pour sortir. L'assiette glisse, puis s'arrête. En rentrant, on raccroche le manteau. Je raccroche. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14840,7 +15774,19 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Tom a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Tom répète tout bas : manteau, sortir, rentrer. On rit un peu. maman n'est pas loin.</t>
+          <t>narrateur|Une assiette de dînette attend sur la commode.
+narrateur|Elle est rose et légère.
+papa|La petite assiette, Mila.
+enfant-f|L'assiette.
+narrateur|Mila la pose dans le panier.
+maman|On fera un stand, tout petit.
+narrateur|Le manteau bleu est fermé.
+papa|Bravo.
+papa|Tu l'as pris pour sortir.
+narrateur|L'assiette glisse, puis s'arrête.
+maman|En rentrant, on raccroche le manteau.
+enfant-f|Je raccroche.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14868,7 +15814,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15036,7 +15982,7 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|On peut y aller le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15064,7 +16010,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le matin. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le matin, l'air est tout frais. Une orange brille dans une caisse. Les pavés sont encore humides. C'est le matin. Le marché s'ouvre. On prend le manteau. La petite tasse tinte, tout doux. Le rideau bouge. La bâche claque, tout loin. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai la tasse. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la chaise. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Il fait frais. Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15204,7 +16150,29 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le matin. La lumière est claire. On écoute jusqu'au bout. Cette fin-là est celle de la chambre, la dînette et le matin. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le matin, l'air est tout frais.
+narrateur|Une orange brille dans une caisse.
+narrateur|Les pavés sont encore humides.
+enfant-f|C'est le matin.
+papa|Le marché s'ouvre.
+papa|On prend le manteau.
+narrateur|La petite tasse tinte, tout doux.
+narrateur|Le rideau bouge.
+narrateur|La bâche claque, tout loin.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai la tasse.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la chaise.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Il fait frais.
+maman|Le manteau te tient chaud.</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr"/>
@@ -15232,7 +16200,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Une caisse d'oranges reste au stand. Mila raccroche le manteau bleu. La dînette reste dans le panier. L'assiette rose est rentrée. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15372,7 +16340,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Une caisse d'oranges reste au stand.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|La dînette reste dans le panier.
+narrateur|L'assiette rose est rentrée.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15400,7 +16377,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint après la sieste. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Après la sieste, les pavés sont chauds. Un store fait une ombre douce. Le marché est plus calme. Après la sieste. On ressort. On reprend le manteau. La petite tasse tinte, tout doux. Le rideau bouge. La bâche claque, tout loin. Ils marchent vers le marché. Mila a le manteau bleu. Tu as pris ton manteau avant de sortir. J'ai la tasse. Bravo. C'est du bon travail. Ils rentrent un moment. Le crochet, Mila. Près de la chaise. Mila raccroche le manteau bleu. Tu as raccroché. Bravo. Le soleil est là. Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15540,7 +16517,29 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint après la sieste. Il y a des miettes sur la table. On attend son tour. Cette fin-là est celle de la chambre, la dînette et après la sieste. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Après la sieste, les pavés sont chauds.
+narrateur|Un store fait une ombre douce.
+narrateur|Le marché est plus calme.
+enfant-f|Après la sieste.
+papa|On ressort.
+papa|On reprend le manteau.
+narrateur|La petite tasse tinte, tout doux.
+narrateur|Le rideau bouge.
+narrateur|La bâche claque, tout loin.
+narrateur|Ils marchent vers le marché.
+narrateur|Mila a le manteau bleu.
+maman|Tu as pris ton manteau avant de sortir.
+enfant-f|J'ai la tasse.
+papa|Bravo.
+papa|C'est du bon travail.
+narrateur|Ils rentrent un moment.
+maman|Le crochet, Mila.
+maman|Près de la chaise.
+narrateur|Mila raccroche le manteau bleu.
+papa|Tu as raccroché.
+papa|Bravo.
+maman|Le soleil est là.
+maman|Le manteau reste fermé.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15568,7 +16567,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'ombre du store recule un peu. Mila raccroche le manteau bleu. La dînette reste dans le panier. Le capuchon bleu pend droit. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15708,7 +16707,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'ombre du store recule un peu.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|La dînette reste dans le panier.
+narrateur|Le capuchon bleu pend droit.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15736,7 +16744,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Tom rejoint le soir. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>Le soir, le ciel devient rose. Une lampe s'allume au stand. Les caisses s'empilent, tout doux. C'est le soir. On rentre bientôt. On raccroche après. La petite tasse tinte, tout doux. Le rideau bouge. La bâche claque, tout loin. Ils rentrent. La chambre est calme. Mila a encore le manteau bleu. On rentre. On raccroche le manteau. J'ai la tasse. Le crochet, Mila. Près de la chaise. Mila raccroche le manteau bleu. Bravo. Tu as raccroché. Il commence à faire frais. On rentre. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15876,7 +16884,29 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Tom rejoint le soir. Un chat miaule une fois. On montre du doigt, sans courir. Cette fin-là est celle de la chambre, la dînette et le soir. Tom a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Tom a entendu : manteau, sortir, rentrer. Tom dit merci à papa. On rentre.</t>
+          <t>narrateur|Le soir, le ciel devient rose.
+narrateur|Une lampe s'allume au stand.
+narrateur|Les caisses s'empilent, tout doux.
+enfant-f|C'est le soir.
+papa|On rentre bientôt.
+papa|On raccroche après.
+narrateur|La petite tasse tinte, tout doux.
+narrateur|Le rideau bouge.
+narrateur|La bâche claque, tout loin.
+narrateur|Ils rentrent.
+narrateur|La chambre est calme.
+narrateur|Mila a encore le manteau bleu.
+papa|On rentre.
+papa|On raccroche le manteau.
+enfant-f|J'ai la tasse.
+maman|Le crochet, Mila.
+maman|Près de la chaise.
+narrateur|Mila raccroche le manteau bleu.
+maman|Bravo.
+maman|Tu as raccroché.
+maman|Il commence à faire frais.
+maman|On rentre.
+papa|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15904,7 +16934,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>La lampe du stand s'éteint. Mila raccroche le manteau bleu. La dînette reste dans le panier. La commode est calme. Bravo, Mila. Tu as pris le manteau. Tu l'as raccroché. Merci. On a bien sorti, et on a bien rentré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16044,7 +17074,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|La lampe du stand s'éteint.
+narrateur|Mila raccroche le manteau bleu.
+narrateur|La dînette reste dans le panier.
+narrateur|La commode est calme.
+maman|Bravo, Mila.
+papa|Tu as pris le manteau.
+papa|Tu l'as raccroché.
+enfant-f|Merci.
+maman|On a bien sorti, et on a bien rentré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16066,7 +17105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16104,6 +17143,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-027.xlsx
+++ b/stories/arbres/TREE-AUT-027.xlsx
@@ -2753,17 +2753,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose un cube, près de la caisse froide. Les carreaux de la cuisine restent dans ses pieds. Un cube attrape un reflet d'orange, au stand.</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose un cube, près de la caisse froide. Un froid de carreaux reste sous ses chaussons. Un cube attrape un reflet d'orange, au stand.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose un cube, près de la caisse froide. Les carreaux de la cuisine restent dans ses pieds. Un cube attrape un reflet d'orange, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose un cube, près de la caisse froide. Un froid de carreaux reste sous ses chaussons. Un cube attrape un reflet d'orange, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose un cube, près de la caisse froide. Les carreaux de la cuisine restent dans ses pieds. Un cube attrape un reflet d'orange, au stand. [pause]</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose un cube, près de la caisse froide. Un froid de carreaux reste sous ses chaussons. Un cube attrape un reflet d'orange, au stand. [pause]</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
@@ -2910,8 +2910,8 @@
 narrateur|Elle soulève le pan, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, toute ronde.
-narrateur|Elle pose un cube, près de la caisse froide.
-narrateur|Les carreaux de la cuisine restent dans ses pieds.
+enfant-f|Je pose un cube, près de la caisse froide.
+narrateur|Un froid de carreaux reste sous ses chaussons.
 narrateur|Un cube attrape un reflet d'orange, au stand.</t>
         </is>
       </c>
@@ -3132,17 +3132,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose un cube, près de la chaise tiède. L'odeur de menthe de l'évier la suit. Un cube attrape un reflet d'orange, au stand.</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose un cube, près de la chaise tiède. L'odeur de menthe de l'évier la suit. Un cube attrape un reflet d'orange, au stand.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose un cube, près de la chaise tiède. L'odeur de menthe de l'évier la suit. Un cube attrape un reflet d'orange, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose un cube, près de la chaise tiède. L'odeur de menthe de l'évier la suit. Un cube attrape un reflet d'orange, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose un cube, près de la chaise tiède. L'odeur de menthe de l'évier la suit. Un cube attrape un reflet d'orange, au stand. [pause]</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose un cube, près de la chaise tiède. L'odeur de menthe de l'évier la suit. Un cube attrape un reflet d'orange, au stand. [pause]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3289,7 +3289,7 @@
 narrateur|Elle soulève le col, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, un peu chaude.
-narrateur|Elle pose un cube, près de la chaise tiède.
+enfant-f|Je pose un cube, près de la chaise tiède.
 narrateur|L'odeur de menthe de l'évier la suit.
 narrateur|Un cube attrape un reflet d'orange, au stand.</t>
         </is>
@@ -3511,17 +3511,17 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose un cube, près de la caisse des lampes. Le col ouvert de la cuisine tient chaud. Un cube attrape un reflet d'orange, au stand.</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose un cube, près de la caisse des lampes. Le col ouvert lui tient chaud, dehors. Un cube attrape un reflet d'orange, au stand.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose un cube, près de la caisse des lampes. Le col ouvert de la cuisine tient chaud. Un cube attrape un reflet d'orange, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose un cube, près de la caisse des lampes. Le col ouvert lui tient chaud, dehors. Un cube attrape un reflet d'orange, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose un cube, près de la caisse des lampes. Le col ouvert de la cuisine tient chaud. Un cube attrape un reflet d'orange, au stand. [pause]</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose un cube, près de la caisse des lampes. Le col ouvert lui tient chaud, dehors. Un cube attrape un reflet d'orange, au stand. [pause]</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
@@ -3668,8 +3668,8 @@
 narrateur|Elle soulève le pli, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, parfumée.
-narrateur|Elle pose un cube, près de la caisse des lampes.
-narrateur|Le col ouvert de la cuisine tient chaud.
+enfant-f|Je pose un cube, près de la caisse des lampes.
+narrateur|Le col ouvert lui tient chaud, dehors.
 narrateur|Un cube attrape un reflet d'orange, au stand.</t>
         </is>
       </c>
@@ -4285,17 +4285,17 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle ouvre le livre, près des oranges froides. Les carreaux de la cuisine restent dans ses pieds. Une miette d'orange reste au bord de la page.</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. J'ouvre le livre, près des oranges froides. Un froid de carreaux reste sous ses chaussons. Une miette d'orange reste au bord de la page.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle ouvre le livre, près des oranges froides. Les carreaux de la cuisine restent dans ses pieds. Une miette d'orange reste au bord de la page.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. J'ouvre le livre, près des oranges froides. Un froid de carreaux reste sous ses chaussons. Une miette d'orange reste au bord de la page.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle ouvre le livre, près des oranges froides. Les carreaux de la cuisine restent dans ses pieds. Une miette d'orange reste au bord de la page. [pause]</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. J'ouvre le livre, près des oranges froides. Un froid de carreaux reste sous ses chaussons. Une miette d'orange reste au bord de la page. [pause]</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
@@ -4442,8 +4442,8 @@
 narrateur|Elle soulève le pan, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, toute ronde.
-narrateur|Elle ouvre le livre, près des oranges froides.
-narrateur|Les carreaux de la cuisine restent dans ses pieds.
+enfant-f|J'ouvre le livre, près des oranges froides.
+narrateur|Un froid de carreaux reste sous ses chaussons.
 narrateur|Une miette d'orange reste au bord de la page.</t>
         </is>
       </c>
@@ -4664,17 +4664,17 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle ouvre le livre, près des oranges tièdes. L'odeur de menthe de l'évier la suit. Une miette d'orange reste au bord de la page.</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. J'ouvre le livre, près des oranges tièdes. L'odeur de menthe de l'évier la suit. Une miette d'orange reste au bord de la page.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle ouvre le livre, près des oranges tièdes. L'odeur de menthe de l'évier la suit. Une miette d'orange reste au bord de la page.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. J'ouvre le livre, près des oranges tièdes. L'odeur de menthe de l'évier la suit. Une miette d'orange reste au bord de la page.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle ouvre le livre, près des oranges tièdes. L'odeur de menthe de l'évier la suit. Une miette d'orange reste au bord de la page. [pause]</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. J'ouvre le livre, près des oranges tièdes. L'odeur de menthe de l'évier la suit. Une miette d'orange reste au bord de la page. [pause]</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
@@ -4821,7 +4821,7 @@
 narrateur|Elle soulève le col, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, un peu chaude.
-narrateur|Elle ouvre le livre, près des oranges tièdes.
+enfant-f|J'ouvre le livre, près des oranges tièdes.
 narrateur|L'odeur de menthe de l'évier la suit.
 narrateur|Une miette d'orange reste au bord de la page.</t>
         </is>
@@ -5043,17 +5043,17 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle ouvre le livre, sous les lampes du stand. Le col ouvert de la cuisine tient chaud. Une miette d'orange reste au bord de la page.</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. J'ouvre le livre, sous les lampes du stand. Le col ouvert lui tient chaud, dehors. Une miette d'orange reste au bord de la page.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle ouvre le livre, sous les lampes du stand. Le col ouvert de la cuisine tient chaud. Une miette d'orange reste au bord de la page.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. J'ouvre le livre, sous les lampes du stand. Le col ouvert lui tient chaud, dehors. Une miette d'orange reste au bord de la page.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle ouvre le livre, sous les lampes du stand. Le col ouvert de la cuisine tient chaud. Une miette d'orange reste au bord de la page. [pause]</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. J'ouvre le livre, sous les lampes du stand. Le col ouvert lui tient chaud, dehors. Une miette d'orange reste au bord de la page. [pause]</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
@@ -5200,8 +5200,8 @@
 narrateur|Elle soulève le pli, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, parfumée.
-narrateur|Elle ouvre le livre, sous les lampes du stand.
-narrateur|Le col ouvert de la cuisine tient chaud.
+enfant-f|J'ouvre le livre, sous les lampes du stand.
+narrateur|Le col ouvert lui tient chaud, dehors.
 narrateur|Une miette d'orange reste au bord de la page.</t>
         </is>
       </c>
@@ -5817,17 +5817,17 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose une tasse, près de la caisse froide. Les carreaux de la cuisine restent dans ses pieds. La petite casserole est près du vrai bol, dehors.</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose une tasse, près de la caisse froide. Un froid de carreaux reste sous ses chaussons. La petite casserole est près du vrai bol, dehors.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose une tasse, près de la caisse froide. Les carreaux de la cuisine restent dans ses pieds. La petite casserole est près du vrai bol, dehors.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose une tasse, près de la caisse froide. Un froid de carreaux reste sous ses chaussons. La petite casserole est près du vrai bol, dehors.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose une tasse, près de la caisse froide. Les carreaux de la cuisine restent dans ses pieds. La petite casserole est près du vrai bol, dehors. [pause]</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose une tasse, près de la caisse froide. Un froid de carreaux reste sous ses chaussons. La petite casserole est près du vrai bol, dehors. [pause]</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
@@ -5974,8 +5974,8 @@
 narrateur|Elle soulève le pan, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, toute ronde.
-narrateur|Elle pose une tasse, près de la caisse froide.
-narrateur|Les carreaux de la cuisine restent dans ses pieds.
+enfant-f|Je pose une tasse, près de la caisse froide.
+narrateur|Un froid de carreaux reste sous ses chaussons.
 narrateur|La petite casserole est près du vrai bol, dehors.</t>
         </is>
       </c>
@@ -6196,17 +6196,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose une tasse, près de la chaise tiède. L'odeur de menthe de l'évier la suit. La petite casserole est près du vrai bol, dehors.</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose une tasse, près de la chaise tiède. L'odeur de menthe de l'évier la suit. La petite casserole est près du vrai bol, dehors.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose une tasse, près de la chaise tiède. L'odeur de menthe de l'évier la suit. La petite casserole est près du vrai bol, dehors.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose une tasse, près de la chaise tiède. L'odeur de menthe de l'évier la suit. La petite casserole est près du vrai bol, dehors.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose une tasse, près de la chaise tiède. L'odeur de menthe de l'évier la suit. La petite casserole est près du vrai bol, dehors. [pause]</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose une tasse, près de la chaise tiède. L'odeur de menthe de l'évier la suit. La petite casserole est près du vrai bol, dehors. [pause]</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -6353,7 +6353,7 @@
 narrateur|Elle soulève le col, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, un peu chaude.
-narrateur|Elle pose une tasse, près de la chaise tiède.
+enfant-f|Je pose une tasse, près de la chaise tiède.
 narrateur|L'odeur de menthe de l'évier la suit.
 narrateur|La petite casserole est près du vrai bol, dehors.</t>
         </is>
@@ -6575,17 +6575,17 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose une tasse, sous les lampes du stand. Le col ouvert de la cuisine tient chaud. La petite casserole est près du vrai bol, dehors.</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose une tasse, sous les lampes du stand. Le col ouvert lui tient chaud, dehors. La petite casserole est près du vrai bol, dehors.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose une tasse, sous les lampes du stand. Le col ouvert de la cuisine tient chaud. La petite casserole est près du vrai bol, dehors.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose une tasse, sous les lampes du stand. Le col ouvert lui tient chaud, dehors. La petite casserole est près du vrai bol, dehors.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose une tasse, sous les lampes du stand. Le col ouvert de la cuisine tient chaud. La petite casserole est près du vrai bol, dehors. [pause]</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose une tasse, sous les lampes du stand. Le col ouvert lui tient chaud, dehors. La petite casserole est près du vrai bol, dehors. [pause]</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
@@ -6732,8 +6732,8 @@
 narrateur|Elle soulève le pli, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, parfumée.
-narrateur|Elle pose une tasse, sous les lampes du stand.
-narrateur|Le col ouvert de la cuisine tient chaud.
+enfant-f|Je pose une tasse, sous les lampes du stand.
+narrateur|Le col ouvert lui tient chaud, dehors.
 narrateur|La petite casserole est près du vrai bol, dehors.</t>
         </is>
       </c>
@@ -8109,17 +8109,17 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose un cube, près de la caisse froide. Les bottes font ploc, sur les pavés froids. L'herbe tache un cube, tout vert, au stand.</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose un cube, près de la caisse froide. Les bottes font ploc, sur les pavés froids. L'herbe tache un cube, tout vert, au stand.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose un cube, près de la caisse froide. Les bottes font ploc, sur les pavés froids. L'herbe tache un cube, tout vert, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose un cube, près de la caisse froide. Les bottes font ploc, sur les pavés froids. L'herbe tache un cube, tout vert, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose un cube, près de la caisse froide. Les bottes font ploc, sur les pavés froids. L'herbe tache un cube, tout vert, au stand. [pause]</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose un cube, près de la caisse froide. Les bottes font ploc, sur les pavés froids. L'herbe tache un cube, tout vert, au stand. [pause]</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
@@ -8266,7 +8266,7 @@
 narrateur|Elle soulève le pan, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, toute ronde.
-narrateur|Elle pose un cube, près de la caisse froide.
+enfant-f|Je pose un cube, près de la caisse froide.
 narrateur|Les bottes font ploc, sur les pavés froids.
 narrateur|L'herbe tache un cube, tout vert, au stand.</t>
         </is>
@@ -8488,17 +8488,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose un cube, près de la chaise tiède. La menthe de la poche sent fort, tout vert. L'herbe tache un cube, tout vert, au stand.</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose un cube, près de la chaise tiède. La menthe de la poche sent fort, tout vert. L'herbe tache un cube, tout vert, au stand.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose un cube, près de la chaise tiède. La menthe de la poche sent fort, tout vert. L'herbe tache un cube, tout vert, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose un cube, près de la chaise tiède. La menthe de la poche sent fort, tout vert. L'herbe tache un cube, tout vert, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose un cube, près de la chaise tiède. La menthe de la poche sent fort, tout vert. L'herbe tache un cube, tout vert, au stand. [pause]</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose un cube, près de la chaise tiède. La menthe de la poche sent fort, tout vert. L'herbe tache un cube, tout vert, au stand. [pause]</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -8645,7 +8645,7 @@
 narrateur|Elle soulève le col, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, un peu chaude.
-narrateur|Elle pose un cube, près de la chaise tiède.
+enfant-f|Je pose un cube, près de la chaise tiède.
 narrateur|La menthe de la poche sent fort, tout vert.
 narrateur|L'herbe tache un cube, tout vert, au stand.</t>
         </is>
@@ -8867,17 +8867,17 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose un cube, près de la caisse des lampes. Une goutte du jardin glisse du manteau bleu. L'herbe tache un cube, tout vert, au stand.</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose un cube, près de la caisse des lampes. Une goutte du jardin glisse du manteau bleu. L'herbe tache un cube, tout vert, au stand.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose un cube, près de la caisse des lampes. Une goutte du jardin glisse du manteau bleu. L'herbe tache un cube, tout vert, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose un cube, près de la caisse des lampes. Une goutte du jardin glisse du manteau bleu. L'herbe tache un cube, tout vert, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose un cube, près de la caisse des lampes. Une goutte du jardin glisse du manteau bleu. L'herbe tache un cube, tout vert, au stand. [pause]</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose un cube, près de la caisse des lampes. Une goutte du jardin glisse du manteau bleu. L'herbe tache un cube, tout vert, au stand. [pause]</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
@@ -9024,7 +9024,7 @@
 narrateur|Elle soulève le pli, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, parfumée.
-narrateur|Elle pose un cube, près de la caisse des lampes.
+enfant-f|Je pose un cube, près de la caisse des lampes.
 narrateur|Une goutte du jardin glisse du manteau bleu.
 narrateur|L'herbe tache un cube, tout vert, au stand.</t>
         </is>
@@ -9641,17 +9641,17 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle ouvre le livre, près des oranges froides. Les bottes font ploc, sur les pavés froids. Une vraie feuille de menthe marque la page.</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. J'ouvre le livre, près des oranges froides. Les bottes font ploc, sur les pavés froids. Une vraie feuille de menthe marque la page.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle ouvre le livre, près des oranges froides. Les bottes font ploc, sur les pavés froids. Une vraie feuille de menthe marque la page.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. J'ouvre le livre, près des oranges froides. Les bottes font ploc, sur les pavés froids. Une vraie feuille de menthe marque la page.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle ouvre le livre, près des oranges froides. Les bottes font ploc, sur les pavés froids. Une vraie feuille de menthe marque la page. [pause]</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. J'ouvre le livre, près des oranges froides. Les bottes font ploc, sur les pavés froids. Une vraie feuille de menthe marque la page. [pause]</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr"/>
@@ -9798,7 +9798,7 @@
 narrateur|Elle soulève le pan, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, toute ronde.
-narrateur|Elle ouvre le livre, près des oranges froides.
+enfant-f|J'ouvre le livre, près des oranges froides.
 narrateur|Les bottes font ploc, sur les pavés froids.
 narrateur|Une vraie feuille de menthe marque la page.</t>
         </is>
@@ -10020,17 +10020,17 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle ouvre le livre, près des oranges tièdes. La menthe de la poche sent fort, tout vert. Une vraie feuille de menthe marque la page.</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. J'ouvre le livre, près des oranges tièdes. La menthe de la poche sent fort, tout vert. Une vraie feuille de menthe marque la page.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle ouvre le livre, près des oranges tièdes. La menthe de la poche sent fort, tout vert. Une vraie feuille de menthe marque la page.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. J'ouvre le livre, près des oranges tièdes. La menthe de la poche sent fort, tout vert. Une vraie feuille de menthe marque la page.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle ouvre le livre, près des oranges tièdes. La menthe de la poche sent fort, tout vert. Une vraie feuille de menthe marque la page. [pause]</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. J'ouvre le livre, près des oranges tièdes. La menthe de la poche sent fort, tout vert. Une vraie feuille de menthe marque la page. [pause]</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr"/>
@@ -10177,7 +10177,7 @@
 narrateur|Elle soulève le col, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, un peu chaude.
-narrateur|Elle ouvre le livre, près des oranges tièdes.
+enfant-f|J'ouvre le livre, près des oranges tièdes.
 narrateur|La menthe de la poche sent fort, tout vert.
 narrateur|Une vraie feuille de menthe marque la page.</t>
         </is>
@@ -10399,17 +10399,17 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle ouvre le livre, sous les lampes du stand. Une goutte du jardin glisse du manteau bleu. Une vraie feuille de menthe marque la page.</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. J'ouvre le livre, sous les lampes du stand. Une goutte du jardin glisse du manteau bleu. Une vraie feuille de menthe marque la page.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle ouvre le livre, sous les lampes du stand. Une goutte du jardin glisse du manteau bleu. Une vraie feuille de menthe marque la page.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. J'ouvre le livre, sous les lampes du stand. Une goutte du jardin glisse du manteau bleu. Une vraie feuille de menthe marque la page.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle ouvre le livre, sous les lampes du stand. Une goutte du jardin glisse du manteau bleu. Une vraie feuille de menthe marque la page. [pause]</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. J'ouvre le livre, sous les lampes du stand. Une goutte du jardin glisse du manteau bleu. Une vraie feuille de menthe marque la page. [pause]</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr"/>
@@ -10556,7 +10556,7 @@
 narrateur|Elle soulève le pli, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, parfumée.
-narrateur|Elle ouvre le livre, sous les lampes du stand.
+enfant-f|J'ouvre le livre, sous les lampes du stand.
 narrateur|Une goutte du jardin glisse du manteau bleu.
 narrateur|Une vraie feuille de menthe marque la page.</t>
         </is>
@@ -11173,17 +11173,17 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose une tasse, près de la caisse froide. Les bottes font ploc, sur les pavés froids. Une goutte perle au bord de l'assiette, dehors.</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose une tasse, près de la caisse froide. Les bottes font ploc, sur les pavés froids. Une goutte perle au bord de l'assiette, dehors.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose une tasse, près de la caisse froide. Les bottes font ploc, sur les pavés froids. Une goutte perle au bord de l'assiette, dehors.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose une tasse, près de la caisse froide. Les bottes font ploc, sur les pavés froids. Une goutte perle au bord de l'assiette, dehors.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose une tasse, près de la caisse froide. Les bottes font ploc, sur les pavés froids. Une goutte perle au bord de l'assiette, dehors. [pause]</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose une tasse, près de la caisse froide. Les bottes font ploc, sur les pavés froids. Une goutte perle au bord de l'assiette, dehors. [pause]</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr"/>
@@ -11330,7 +11330,7 @@
 narrateur|Elle soulève le pan, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, toute ronde.
-narrateur|Elle pose une tasse, près de la caisse froide.
+enfant-f|Je pose une tasse, près de la caisse froide.
 narrateur|Les bottes font ploc, sur les pavés froids.
 narrateur|Une goutte perle au bord de l'assiette, dehors.</t>
         </is>
@@ -11552,17 +11552,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose une tasse, près de la chaise tiède. La menthe de la poche sent fort, tout vert. Une goutte perle au bord de l'assiette, dehors.</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose une tasse, près de la chaise tiède. La menthe de la poche sent fort, tout vert. Une goutte perle au bord de l'assiette, dehors.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose une tasse, près de la chaise tiède. La menthe de la poche sent fort, tout vert. Une goutte perle au bord de l'assiette, dehors.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose une tasse, près de la chaise tiède. La menthe de la poche sent fort, tout vert. Une goutte perle au bord de l'assiette, dehors.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose une tasse, près de la chaise tiède. La menthe de la poche sent fort, tout vert. Une goutte perle au bord de l'assiette, dehors. [pause]</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose une tasse, près de la chaise tiède. La menthe de la poche sent fort, tout vert. Une goutte perle au bord de l'assiette, dehors. [pause]</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -11709,7 +11709,7 @@
 narrateur|Elle soulève le col, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, un peu chaude.
-narrateur|Elle pose une tasse, près de la chaise tiède.
+enfant-f|Je pose une tasse, près de la chaise tiède.
 narrateur|La menthe de la poche sent fort, tout vert.
 narrateur|Une goutte perle au bord de l'assiette, dehors.</t>
         </is>
@@ -11931,17 +11931,17 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose une tasse, sous les lampes du stand. Une goutte du jardin glisse du manteau bleu. Une goutte perle au bord de l'assiette, dehors.</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose une tasse, sous les lampes du stand. Une goutte du jardin glisse du manteau bleu. Une goutte perle au bord de l'assiette, dehors.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose une tasse, sous les lampes du stand. Une goutte du jardin glisse du manteau bleu. Une goutte perle au bord de l'assiette, dehors.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose une tasse, sous les lampes du stand. Une goutte du jardin glisse du manteau bleu. Une goutte perle au bord de l'assiette, dehors.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose une tasse, sous les lampes du stand. Une goutte du jardin glisse du manteau bleu. Une goutte perle au bord de l'assiette, dehors. [pause]</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose une tasse, sous les lampes du stand. Une goutte du jardin glisse du manteau bleu. Une goutte perle au bord de l'assiette, dehors. [pause]</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
@@ -12088,7 +12088,7 @@
 narrateur|Elle soulève le pli, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, parfumée.
-narrateur|Elle pose une tasse, sous les lampes du stand.
+enfant-f|Je pose une tasse, sous les lampes du stand.
 narrateur|Une goutte du jardin glisse du manteau bleu.
 narrateur|Une goutte perle au bord de l'assiette, dehors.</t>
         </is>
@@ -13465,17 +13465,17 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose un cube, près de la caisse froide. Le petit panier jouet tapote la caisse. Un cube tapote le parquet, dans sa mémoire.</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose un cube, près de la caisse froide. Le petit panier jouet tapote la caisse. Un cube tapote le parquet, dans sa mémoire.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose un cube, près de la caisse froide. Le petit panier jouet tapote la caisse. Un cube tapote le parquet, dans sa mémoire.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose un cube, près de la caisse froide. Le petit panier jouet tapote la caisse. Un cube tapote le parquet, dans sa mémoire.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose un cube, près de la caisse froide. Le petit panier jouet tapote la caisse. Un cube tapote le parquet, dans sa mémoire. [pause]</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose un cube, près de la caisse froide. Le petit panier jouet tapote la caisse. Un cube tapote le parquet, dans sa mémoire. [pause]</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
 narrateur|Elle soulève le pan, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, toute ronde.
-narrateur|Elle pose un cube, près de la caisse froide.
+enfant-f|Je pose un cube, près de la caisse froide.
 narrateur|Le petit panier jouet tapote la caisse.
 narrateur|Un cube tapote le parquet, dans sa mémoire.</t>
         </is>
@@ -13844,17 +13844,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose un cube, près de la chaise tiède. Le rideau jaune reste derrière, à la maison. Un cube tapote le parquet, dans sa mémoire.</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose un cube, près de la chaise tiède. Le rideau jaune reste derrière, à la maison. Un cube tapote le parquet, dans sa mémoire.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose un cube, près de la chaise tiède. Le rideau jaune reste derrière, à la maison. Un cube tapote le parquet, dans sa mémoire.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose un cube, près de la chaise tiède. Le rideau jaune reste derrière, à la maison. Un cube tapote le parquet, dans sa mémoire.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose un cube, près de la chaise tiède. Le rideau jaune reste derrière, à la maison. Un cube tapote le parquet, dans sa mémoire. [pause]</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose un cube, près de la chaise tiède. Le rideau jaune reste derrière, à la maison. Un cube tapote le parquet, dans sa mémoire. [pause]</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -14001,7 +14001,7 @@
 narrateur|Elle soulève le col, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, un peu chaude.
-narrateur|Elle pose un cube, près de la chaise tiède.
+enfant-f|Je pose un cube, près de la chaise tiède.
 narrateur|Le rideau jaune reste derrière, à la maison.
 narrateur|Un cube tapote le parquet, dans sa mémoire.</t>
         </is>
@@ -14223,17 +14223,17 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose un cube, près de la caisse des lampes. Le savon de la chambre reste sur le col. Un cube tapote le parquet, dans sa mémoire.</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose un cube, près de la caisse des lampes. Le savon de la chambre reste sur le col. Un cube tapote le parquet, dans sa mémoire.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose un cube, près de la caisse des lampes. Le savon de la chambre reste sur le col. Un cube tapote le parquet, dans sa mémoire.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose un cube, près de la caisse des lampes. Le savon de la chambre reste sur le col. Un cube tapote le parquet, dans sa mémoire.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose un cube, près de la caisse des lampes. Le savon de la chambre reste sur le col. Un cube tapote le parquet, dans sa mémoire. [pause]</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose un cube, près de la caisse des lampes. Le savon de la chambre reste sur le col. Un cube tapote le parquet, dans sa mémoire. [pause]</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr"/>
@@ -14380,7 +14380,7 @@
 narrateur|Elle soulève le pli, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, parfumée.
-narrateur|Elle pose un cube, près de la caisse des lampes.
+enfant-f|Je pose un cube, près de la caisse des lampes.
 narrateur|Le savon de la chambre reste sur le col.
 narrateur|Un cube tapote le parquet, dans sa mémoire.</t>
         </is>
@@ -14997,17 +14997,17 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle ouvre le livre, près des oranges froides. Le petit panier jouet tapote la caisse. Le rideau jaune colore la page, au stand.</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. J'ouvre le livre, près des oranges froides. Le petit panier jouet tapote la caisse. Le rideau jaune colore la page, au stand.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle ouvre le livre, près des oranges froides. Le petit panier jouet tapote la caisse. Le rideau jaune colore la page, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. J'ouvre le livre, près des oranges froides. Le petit panier jouet tapote la caisse. Le rideau jaune colore la page, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle ouvre le livre, près des oranges froides. Le petit panier jouet tapote la caisse. Le rideau jaune colore la page, au stand. [pause]</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. J'ouvre le livre, près des oranges froides. Le petit panier jouet tapote la caisse. Le rideau jaune colore la page, au stand. [pause]</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr"/>
@@ -15154,7 +15154,7 @@
 narrateur|Elle soulève le pan, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, toute ronde.
-narrateur|Elle ouvre le livre, près des oranges froides.
+enfant-f|J'ouvre le livre, près des oranges froides.
 narrateur|Le petit panier jouet tapote la caisse.
 narrateur|Le rideau jaune colore la page, au stand.</t>
         </is>
@@ -15376,17 +15376,17 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle ouvre le livre, près des oranges tièdes. Le rideau jaune reste derrière, à la maison. Le rideau jaune colore la page, au stand.</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. J'ouvre le livre, près des oranges tièdes. Le rideau jaune reste derrière, à la maison. Le rideau jaune colore la page, au stand.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle ouvre le livre, près des oranges tièdes. Le rideau jaune reste derrière, à la maison. Le rideau jaune colore la page, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. J'ouvre le livre, près des oranges tièdes. Le rideau jaune reste derrière, à la maison. Le rideau jaune colore la page, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle ouvre le livre, près des oranges tièdes. Le rideau jaune reste derrière, à la maison. Le rideau jaune colore la page, au stand. [pause]</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. J'ouvre le livre, près des oranges tièdes. Le rideau jaune reste derrière, à la maison. Le rideau jaune colore la page, au stand. [pause]</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr"/>
@@ -15533,7 +15533,7 @@
 narrateur|Elle soulève le col, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, un peu chaude.
-narrateur|Elle ouvre le livre, près des oranges tièdes.
+enfant-f|J'ouvre le livre, près des oranges tièdes.
 narrateur|Le rideau jaune reste derrière, à la maison.
 narrateur|Le rideau jaune colore la page, au stand.</t>
         </is>
@@ -15755,17 +15755,17 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle ouvre le livre, sous les lampes du stand. Le savon de la chambre reste sur le col. Le rideau jaune colore la page, au stand.</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. J'ouvre le livre, sous les lampes du stand. Le savon de la chambre reste sur le col. Le rideau jaune colore la page, au stand.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle ouvre le livre, sous les lampes du stand. Le savon de la chambre reste sur le col. Le rideau jaune colore la page, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. J'ouvre le livre, sous les lampes du stand. Le savon de la chambre reste sur le col. Le rideau jaune colore la page, au stand.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle ouvre le livre, sous les lampes du stand. Le savon de la chambre reste sur le col. Le rideau jaune colore la page, au stand. [pause]</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. J'ouvre le livre, sous les lampes du stand. Le savon de la chambre reste sur le col. Le rideau jaune colore la page, au stand. [pause]</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr"/>
@@ -15912,7 +15912,7 @@
 narrateur|Elle soulève le pli, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, parfumée.
-narrateur|Elle ouvre le livre, sous les lampes du stand.
+enfant-f|J'ouvre le livre, sous les lampes du stand.
 narrateur|Le savon de la chambre reste sur le col.
 narrateur|Le rideau jaune colore la page, au stand.</t>
         </is>
@@ -16529,17 +16529,17 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose une tasse, près de la caisse froide. Le petit panier jouet tapote la caisse. La petite tasse est près du lit, dans sa poche.</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose une tasse, près de la caisse froide. Le petit panier jouet tapote la caisse. La petite tasse est près du lit, dans sa poche.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose une tasse, près de la caisse froide. Le petit panier jouet tapote la caisse. La petite tasse est près du lit, dans sa poche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose une tasse, près de la caisse froide. Le petit panier jouet tapote la caisse. La petite tasse est près du lit, dans sa poche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Elle pose une tasse, près de la caisse froide. Le petit panier jouet tapote la caisse. La petite tasse est près du lit, dans sa poche. [pause]</t>
+          <t>Le marché s'ouvre, ce matin. Ils sortent, et l'air pique le nez. Mila pose le manteau sur une caisse. J'en prends une, vite ! La bâche se déroule, et recouvre le bleu. Il est sous la bâche, je le vois ! Elle saisit un pan rayé, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous la bâche. L'entaille, je la vois. Elle soulève le pan, sans tirer. Une orange, pour le panier. Mila la choisit, toute ronde. Je pose une tasse, près de la caisse froide. Le petit panier jouet tapote la caisse. La petite tasse est près du lit, dans sa poche. [pause]</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
@@ -16686,7 +16686,7 @@
 narrateur|Elle soulève le pan, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, toute ronde.
-narrateur|Elle pose une tasse, près de la caisse froide.
+enfant-f|Je pose une tasse, près de la caisse froide.
 narrateur|Le petit panier jouet tapote la caisse.
 narrateur|La petite tasse est près du lit, dans sa poche.</t>
         </is>
@@ -16908,17 +16908,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose une tasse, près de la chaise tiède. Le rideau jaune reste derrière, à la maison. La petite tasse est près du lit, dans sa poche.</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose une tasse, près de la chaise tiède. Le rideau jaune reste derrière, à la maison. La petite tasse est près du lit, dans sa poche.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose une tasse, près de la chaise tiède. Le rideau jaune reste derrière, à la maison. La petite tasse est près du lit, dans sa poche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose une tasse, près de la chaise tiède. Le rideau jaune reste derrière, à la maison. La petite tasse est près du lit, dans sa poche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Elle pose une tasse, près de la chaise tiède. Le rideau jaune reste derrière, à la maison. La petite tasse est près du lit, dans sa poche. [pause]</t>
+          <t>Le marché est plus calme, après la sieste. Ils sortent, et les pavés sont tièdes. Mila pose le manteau sur une chaise. J'en prends une, tiède ! Un sac bleu pend, à côté de la chaise. Il est là, je le vois ! Elle saisit le sac, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, sous le store. L'entaille, je la vois. Elle soulève le col, sans tirer. Une orange, pour le panier. Mila la choisit, un peu chaude. Je pose une tasse, près de la chaise tiède. Le rideau jaune reste derrière, à la maison. La petite tasse est près du lit, dans sa poche. [pause]</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -17065,7 +17065,7 @@
 narrateur|Elle soulève le col, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, un peu chaude.
-narrateur|Elle pose une tasse, près de la chaise tiède.
+enfant-f|Je pose une tasse, près de la chaise tiède.
 narrateur|Le rideau jaune reste derrière, à la maison.
 narrateur|La petite tasse est près du lit, dans sa poche.</t>
         </is>
@@ -17287,17 +17287,17 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose une tasse, sous les lampes du stand. Le savon de la chambre reste sur le col. La petite tasse est près du lit, dans sa poche.</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le bouton à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose une tasse, sous les lampes du stand. Le savon de la chambre reste sur le col. La petite tasse est près du lit, dans sa poche.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose une tasse, sous les lampes du stand. Le savon de la chambre reste sur le col. La petite tasse est près du lit, dans sa poche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis level="moderate"&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose une tasse, sous les lampes du stand. Le savon de la chambre reste sur le col. La petite tasse est près du lit, dans sa poche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Elle pose une tasse, sous les lampes du stand. Le savon de la chambre reste sur le col. La petite tasse est près du lit, dans sa poche. [pause]</t>
+          <t>Le marché se range, ce soir. Ils sortent, et la vitre est bleue. Mila pose le manteau près de la caisse. J'en prends une, avant le pli ! La bâche se plie, et avale le bleu. Il est dans le pli, je le vois ! Elle tire le pli, trop vite. Cette fois, elle refuse de foncer. Le &lt;emphasis&gt;bouton&lt;/emphasis&gt; à lune fait toc, dans la bâche. L'entaille, je la vois. Elle soulève le pli, sans tirer. Une orange, pour le panier. Mila la choisit, parfumée. Je pose une tasse, sous les lampes du stand. Le savon de la chambre reste sur le col. La petite tasse est près du lit, dans sa poche. [pause]</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr"/>
@@ -17444,7 +17444,7 @@
 narrateur|Elle soulève le pli, sans tirer.
 papa|Une orange, pour le panier.
 narrateur|Mila la choisit, parfumée.
-narrateur|Elle pose une tasse, sous les lampes du stand.
+enfant-f|Je pose une tasse, sous les lampes du stand.
 narrateur|Le savon de la chambre reste sur le col.
 narrateur|La petite tasse est près du lit, dans sa poche.</t>
         </is>
@@ -17660,7 +17660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17724,6 +17724,13 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
